--- a/src/ExcelsiorAspose.Tests/LinkTests.UrlOnly.verified.xlsx
+++ b/src/ExcelsiorAspose.Tests/LinkTests.UrlOnly.verified.xlsx
@@ -640,8 +640,9 @@
   </sheetData>
   <autoFilter ref="A1:F2"/>
   <hyperlinks>
-    <hyperlink ref="B2" r:id="DeterministicId2" display="https://google.com"/>
+    <hyperlink ref="B2" r:id="DeterministicId3" display="https://google.com"/>
     <hyperlink ref="C2" r:id="DeterministicId1" display="https://github.com"/>
+    <hyperlink ref="F2" r:id="DeterministicId2" display="● https://google.com"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/src/ExcelsiorAspose.Tests/LinkTests.UrlOnly.verified.xlsx
+++ b/src/ExcelsiorAspose.Tests/LinkTests.UrlOnly.verified.xlsx
@@ -640,9 +640,9 @@
   </sheetData>
   <autoFilter ref="A1:F2"/>
   <hyperlinks>
-    <hyperlink ref="B2" r:id="DeterministicId3" display="https://google.com"/>
+    <hyperlink ref="B2" r:id="DeterministicId2" display="https://google.com"/>
     <hyperlink ref="C2" r:id="DeterministicId1" display="https://github.com"/>
-    <hyperlink ref="F2" r:id="DeterministicId2" display="● https://google.com"/>
+    <hyperlink ref="F2" r:id="DeterministicId3" display="● https://google.com"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/src/ExcelsiorAspose.Tests/LinkTests.UrlOnly.verified.xlsx
+++ b/src/ExcelsiorAspose.Tests/LinkTests.UrlOnly.verified.xlsx
@@ -49,9 +49,8 @@
     <r>
       <rPr>
         <b/>
-        <u val="single"/>
         <sz val="10"/>
-        <color rgb="FF0000FF"/>
+        <color theme="1"/>
         <rFont val="Arial"/>
         <family val="2"/>
       </rPr>
@@ -80,9 +79,8 @@
     <r>
       <rPr>
         <b/>
-        <u val="single"/>
         <sz val="10"/>
-        <color rgb="FF0000FF"/>
+        <color theme="1"/>
         <rFont val="Arial"/>
         <family val="2"/>
       </rPr>
@@ -103,9 +101,8 @@
     <r>
       <rPr>
         <b/>
-        <u val="single"/>
         <sz val="10"/>
-        <color rgb="FF0000FF"/>
+        <color theme="1"/>
         <rFont val="Arial"/>
         <family val="2"/>
       </rPr>
@@ -127,7 +124,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="4">
+  <fonts count="3">
     <font>
       <sz val="10"/>
       <color theme="1"/>
@@ -145,14 +142,6 @@
       <b/>
       <sz val="10"/>
       <color theme="1"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <b/>
-      <u val="single"/>
-      <sz val="10"/>
-      <color rgb="FF0000FF"/>
       <name val="Arial"/>
       <family val="2"/>
     </font>

--- a/src/ExcelsiorAspose.Tests/LinkTests.UrlOnly.verified.xlsx
+++ b/src/ExcelsiorAspose.Tests/LinkTests.UrlOnly.verified.xlsx
@@ -588,7 +588,7 @@
     <col min="6" max="6" width="24.7142857142857" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="14" customHeight="1">
+    <row r="1" spans="1:6" ht="16" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -608,7 +608,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:6" ht="27" customHeight="1">
+    <row r="2" spans="1:6" ht="26" customHeight="1">
       <c r="A2" s="2" t="s">
         <v>6</v>
       </c>

--- a/src/ExcelsiorAspose.Tests/LinkTests.UrlOnly.verified.xlsx
+++ b/src/ExcelsiorAspose.Tests/LinkTests.UrlOnly.verified.xlsx
@@ -588,7 +588,7 @@
     <col min="6" max="6" width="24.7142857142857" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="16" customHeight="1">
+    <row r="1" spans="1:6" ht="14" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -608,7 +608,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:6" ht="26" customHeight="1">
+    <row r="2" spans="1:6" ht="27" customHeight="1">
       <c r="A2" s="2" t="s">
         <v>6</v>
       </c>

--- a/src/ExcelsiorAspose.Tests/LinkTests.UrlOnly.verified.xlsx
+++ b/src/ExcelsiorAspose.Tests/LinkTests.UrlOnly.verified.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Sheet1" sheetId="2" r:id="DeterministicId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$F$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$C$2</definedName>
   </definedNames>
   <calcPr fullCalcOnLoad="1"/>
 </workbook>
@@ -584,7 +584,7 @@
     <col min="2" max="2" width="17.7142857142857" customWidth="1"/>
     <col min="3" max="3" width="16.7142857142857" customWidth="1"/>
     <col min="4" max="4" width="24.7142857142857" customWidth="1"/>
-    <col min="5" max="5" width="22.7142857142857" customWidth="1"/>
+    <col min="5" max="5" width="19.7142857142857" customWidth="1"/>
     <col min="6" max="6" width="24.7142857142857" customWidth="1"/>
   </cols>
   <sheetData>
@@ -627,7 +627,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F2"/>
+  <autoFilter ref="A1:C2"/>
   <hyperlinks>
     <hyperlink ref="B2" r:id="DeterministicId2" display="https://google.com"/>
     <hyperlink ref="C2" r:id="DeterministicId1" display="https://github.com"/>
